--- a/excel-templates/student-import-template.xlsx
+++ b/excel-templates/student-import-template.xlsx
@@ -1,41 +1,143 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Desktop/schoolwebsite/inddia-erp/excel-templates/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A5559B-5AC2-1F47-B9D5-4AC6FD38F962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Student Import" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+  <si>
+    <t>studentName</t>
+  </si>
+  <si>
+    <t>photoUrl</t>
+  </si>
+  <si>
+    <t>schoolId</t>
+  </si>
+  <si>
+    <t>className</t>
+  </si>
+  <si>
+    <t>section</t>
+  </si>
+  <si>
+    <t>admissionDate</t>
+  </si>
+  <si>
+    <t>discountFee</t>
+  </si>
+  <si>
+    <t>studentAadharNumber</t>
+  </si>
+  <si>
+    <t>studentPassword</t>
+  </si>
+  <si>
+    <t>dateOfBirth</t>
+  </si>
+  <si>
+    <t>birthId</t>
+  </si>
+  <si>
+    <t>isOrphan</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>caste</t>
+  </si>
+  <si>
+    <t>osc</t>
+  </si>
+  <si>
+    <t>identificationMark</t>
+  </si>
+  <si>
+    <t>previousSchool</t>
+  </si>
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>bloodGroup</t>
+  </si>
+  <si>
+    <t>previousBoardRollNo</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>fatherName</t>
+  </si>
+  <si>
+    <t>fatherAadharNumber</t>
+  </si>
+  <si>
+    <t>fatherOccupation</t>
+  </si>
+  <si>
+    <t>fatherEducation</t>
+  </si>
+  <si>
+    <t>fatherMobileNumber</t>
+  </si>
+  <si>
+    <t>fatherProfession</t>
+  </si>
+  <si>
+    <t>fatherIncome</t>
+  </si>
+  <si>
+    <t>fatherEmail</t>
+  </si>
+  <si>
+    <t>fatherPassword</t>
+  </si>
+  <si>
+    <t>motherName</t>
+  </si>
+  <si>
+    <t>motherAadharNumber</t>
+  </si>
+  <si>
+    <t>motherOccupation</t>
+  </si>
+  <si>
+    <t>motherEducation</t>
+  </si>
+  <si>
+    <t>motherMobileNumber</t>
+  </si>
+  <si>
+    <t>motherProfession</t>
+  </si>
+  <si>
+    <t>motherIncome</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +167,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,238 +506,127 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AK1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>studentName</v>
-      </c>
-      <c r="B1" t="str">
-        <v>photoUrl</v>
-      </c>
-      <c r="C1" t="str">
-        <v>schoolId</v>
-      </c>
-      <c r="D1" t="str">
-        <v>className</v>
-      </c>
-      <c r="E1" t="str">
-        <v>section</v>
-      </c>
-      <c r="F1" t="str">
-        <v>admissionDate</v>
-      </c>
-      <c r="G1" t="str">
-        <v>discountFee</v>
-      </c>
-      <c r="H1" t="str">
-        <v>studentAadharNumber</v>
-      </c>
-      <c r="I1" t="str">
-        <v>studentPassword</v>
-      </c>
-      <c r="J1" t="str">
-        <v>dateOfBirth</v>
-      </c>
-      <c r="K1" t="str">
-        <v>birthId</v>
-      </c>
-      <c r="L1" t="str">
-        <v>isOrphan</v>
-      </c>
-      <c r="M1" t="str">
-        <v>gender</v>
-      </c>
-      <c r="N1" t="str">
-        <v>caste</v>
-      </c>
-      <c r="O1" t="str">
-        <v>osc</v>
-      </c>
-      <c r="P1" t="str">
-        <v>identificationMark</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>previousSchool</v>
-      </c>
-      <c r="R1" t="str">
-        <v>region</v>
-      </c>
-      <c r="S1" t="str">
-        <v>bloodGroup</v>
-      </c>
-      <c r="T1" t="str">
-        <v>previousBoardRollNo</v>
-      </c>
-      <c r="U1" t="str">
-        <v>address</v>
-      </c>
-      <c r="V1" t="str">
-        <v>fatherName</v>
-      </c>
-      <c r="W1" t="str">
-        <v>fatherAadharNumber</v>
-      </c>
-      <c r="X1" t="str">
-        <v>fatherOccupation</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>fatherEducation</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>fatherMobileNumber</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>fatherProfession</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>fatherIncome</v>
-      </c>
-      <c r="AC1" t="str">
-        <v>fatherEmail</v>
-      </c>
-      <c r="AD1" t="str">
-        <v>fatherPassword</v>
-      </c>
-      <c r="AE1" t="str">
-        <v>motherName</v>
-      </c>
-      <c r="AF1" t="str">
-        <v>motherAadharNumber</v>
-      </c>
-      <c r="AG1" t="str">
-        <v>motherOccupation</v>
-      </c>
-      <c r="AH1" t="str">
-        <v>motherEducation</v>
-      </c>
-      <c r="AI1" t="str">
-        <v>motherMobileNumber</v>
-      </c>
-      <c r="AJ1" t="str">
-        <v>motherProfession</v>
-      </c>
-      <c r="AK1" t="str">
-        <v>motherIncome</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Rahul Kumar</v>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v>STU-1001</v>
-      </c>
-      <c r="D2" t="str">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="str">
-        <v>A</v>
-      </c>
-      <c r="F2" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="G2" t="str">
-        <v>0</v>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v>Student@123</v>
-      </c>
-      <c r="J2" t="str">
-        <v>2012-01-15</v>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v>false</v>
-      </c>
-      <c r="M2" t="str">
-        <v>Male</v>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v/>
-      </c>
-      <c r="R2" t="str">
-        <v>Urban</v>
-      </c>
-      <c r="S2" t="str">
-        <v>O+</v>
-      </c>
-      <c r="T2" t="str">
-        <v/>
-      </c>
-      <c r="U2" t="str">
-        <v>Main Street</v>
-      </c>
-      <c r="V2" t="str">
-        <v>Raj Kumar</v>
-      </c>
-      <c r="W2" t="str">
-        <v/>
-      </c>
-      <c r="X2" t="str">
-        <v/>
-      </c>
-      <c r="Y2" t="str">
-        <v/>
-      </c>
-      <c r="Z2" t="str">
-        <v>9876543210</v>
-      </c>
-      <c r="AA2" t="str">
-        <v/>
-      </c>
-      <c r="AB2" t="str">
-        <v/>
-      </c>
-      <c r="AC2" t="str">
-        <v>raj.kumar@example.com</v>
-      </c>
-      <c r="AD2" t="str">
-        <v>Parent@123</v>
-      </c>
-      <c r="AE2" t="str">
-        <v>Sita Kumari</v>
-      </c>
-      <c r="AF2" t="str">
-        <v/>
-      </c>
-      <c r="AG2" t="str">
-        <v/>
-      </c>
-      <c r="AH2" t="str">
-        <v/>
-      </c>
-      <c r="AI2" t="str">
-        <v>9876500000</v>
-      </c>
-      <c r="AJ2" t="str">
-        <v/>
-      </c>
-      <c r="AK2" t="str">
-        <v/>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AK2"/>
+    <ignoredError sqref="A1:AK1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>